--- a/tool/Population/data/PopulationTest.xlsx
+++ b/tool/Population/data/PopulationTest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29930"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29931"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HydroTools\tool\Population\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4A51987-A10E-4B85-9D1E-34D0F28B18CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFEBF8E6-463D-4818-85DA-50567F2968D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28898" yWindow="6368" windowWidth="28996" windowHeight="15675" xr2:uid="{1806D99B-D834-4FFC-97CD-8FB49E502DB0}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{1806D99B-D834-4FFC-97CD-8FB49E502DB0}"/>
   </bookViews>
   <sheets>
     <sheet name="Population" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="29">
   <si>
     <t>DANE</t>
   </si>
@@ -89,9 +89,6 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>DANE old reports. PUrban as 85% from total based on oficial census data.</t>
-  </si>
-  <si>
     <t>CountryName</t>
   </si>
   <si>
@@ -114,6 +111,21 @@
   </si>
   <si>
     <t>San Luis De Gaceno</t>
+  </si>
+  <si>
+    <t>DANE old reports. PUrban as 85% from total based on official census data.</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Bogotá, D.C.</t>
+  </si>
+  <si>
+    <t>11001</t>
+  </si>
+  <si>
+    <t>DANE old reports. PUrban as 99.8% from total based on official census data.</t>
   </si>
 </sst>
 </file>
@@ -492,15 +504,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59748B6C-D14F-4E94-B3A5-8F6624F8A8E2}">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="3" width="9.06640625" style="1"/>
     <col min="4" max="4" width="16.33203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="9.06640625" style="1"/>
-    <col min="6" max="6" width="20" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="9.06640625" style="1"/>
-    <col min="8" max="8" width="16.33203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20" style="1" customWidth="1"/>
     <col min="9" max="11" width="9.06640625" style="1"/>
     <col min="12" max="12" width="61.59765625" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="9.06640625" style="1"/>
@@ -514,22 +526,22 @@
         <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>12</v>
@@ -552,22 +564,22 @@
         <v>1993</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="I2" s="1">
         <v>69695</v>
@@ -587,22 +599,22 @@
         <v>1995</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="I3" s="1">
         <v>78923</v>
@@ -616,7 +628,7 @@
         <v>11838</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.6">
@@ -627,22 +639,22 @@
         <v>2005</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="I4" s="1">
         <v>101551</v>
@@ -662,22 +674,22 @@
         <v>2017</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="I5" s="1">
         <v>118267</v>
@@ -691,7 +703,7 @@
         <v>17740</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.6">
@@ -702,22 +714,22 @@
         <v>2018</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="I6" s="1">
         <v>129652</v>
@@ -737,22 +749,22 @@
         <v>1985</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="I7" s="1">
         <v>7371</v>
@@ -772,19 +784,19 @@
         <v>1993</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>23</v>
@@ -807,22 +819,22 @@
         <v>2005</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="I9" s="1">
         <v>6383</v>
@@ -842,19 +854,19 @@
         <v>2018</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>23</v>
@@ -867,12 +879,608 @@
       </c>
       <c r="K10" s="1">
         <v>2409</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1985</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" s="1">
+        <v>4225649</v>
+      </c>
+      <c r="J11" s="1">
+        <v>4216887</v>
+      </c>
+      <c r="K11" s="1">
+        <v>8762</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1993</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" s="1">
+        <v>4945448</v>
+      </c>
+      <c r="J12" s="1">
+        <v>4931796</v>
+      </c>
+      <c r="K12" s="1">
+        <v>13652</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="1">
+        <v>2005</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I13" s="1">
+        <v>6840116</v>
+      </c>
+      <c r="J13" s="1">
+        <v>6824510</v>
+      </c>
+      <c r="K13" s="1">
+        <v>15606</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="1">
+        <v>2018</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14" s="1">
+        <v>7181469</v>
+      </c>
+      <c r="J14" s="1">
+        <v>7166249</v>
+      </c>
+      <c r="K14" s="1">
+        <v>15220</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="1">
+        <v>1775</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I15" s="1">
+        <v>16233</v>
+      </c>
+      <c r="J15" s="1">
+        <v>16201</v>
+      </c>
+      <c r="K15" s="1">
+        <v>32</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="1">
+        <v>1800</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" s="1">
+        <v>21964</v>
+      </c>
+      <c r="J16" s="1">
+        <v>21920</v>
+      </c>
+      <c r="K16" s="1">
+        <v>44</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="1">
+        <v>1832</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I17" s="1">
+        <v>28341</v>
+      </c>
+      <c r="J17" s="1">
+        <v>28284</v>
+      </c>
+      <c r="K17" s="1">
+        <v>57</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="1">
+        <v>1870</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I18" s="1">
+        <v>40883</v>
+      </c>
+      <c r="J18" s="1">
+        <v>40801</v>
+      </c>
+      <c r="K18" s="1">
+        <v>82</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="1">
+        <v>1905</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I19" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J19" s="1">
+        <v>99800</v>
+      </c>
+      <c r="K19" s="1">
+        <v>200</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="1">
+        <v>1912</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I20" s="1">
+        <v>121257</v>
+      </c>
+      <c r="J20" s="1">
+        <v>121014</v>
+      </c>
+      <c r="K20" s="1">
+        <v>243</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="1">
+        <v>1918</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I21" s="1">
+        <v>143994</v>
+      </c>
+      <c r="J21" s="1">
+        <v>143706</v>
+      </c>
+      <c r="K21" s="1">
+        <v>288</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="1">
+        <v>1928</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I22" s="1">
+        <v>235702</v>
+      </c>
+      <c r="J22" s="1">
+        <v>235231</v>
+      </c>
+      <c r="K22" s="1">
+        <v>471</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="1">
+        <v>1938</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I23" s="1">
+        <v>325650</v>
+      </c>
+      <c r="J23" s="1">
+        <v>324999</v>
+      </c>
+      <c r="K23" s="1">
+        <v>651</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="1">
+        <v>1951</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I24" s="1">
+        <v>715250</v>
+      </c>
+      <c r="J24" s="1">
+        <v>713820</v>
+      </c>
+      <c r="K24" s="1">
+        <v>1430</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="1">
+        <v>1964</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I25" s="1">
+        <v>1697311</v>
+      </c>
+      <c r="J25" s="1">
+        <v>1693916</v>
+      </c>
+      <c r="K25" s="1">
+        <v>3395</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="1">
+        <v>1973</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I26" s="1">
+        <v>2855065</v>
+      </c>
+      <c r="J26" s="1">
+        <v>2849355</v>
+      </c>
+      <c r="K26" s="1">
+        <v>5710</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K6" xr:uid="{59748B6C-D14F-4E94-B3A5-8F6624F8A8E2}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L6">
-    <sortCondition ref="E2:E6"/>
+    <sortCondition ref="G2:G6"/>
     <sortCondition ref="B2:B6"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tool/Population/data/PopulationTest.xlsx
+++ b/tool/Population/data/PopulationTest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HydroTools\tool\Population\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFEBF8E6-463D-4818-85DA-50567F2968D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF18DF1C-F7F4-462A-9825-90D46B7CEBAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{1806D99B-D834-4FFC-97CD-8FB49E502DB0}"/>
+    <workbookView xWindow="-28898" yWindow="6368" windowWidth="28996" windowHeight="15675" xr2:uid="{1806D99B-D834-4FFC-97CD-8FB49E502DB0}"/>
   </bookViews>
   <sheets>
     <sheet name="Population" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="28">
   <si>
     <t>DANE</t>
   </si>
@@ -93,9 +93,6 @@
   </si>
   <si>
     <t>CountryID</t>
-  </si>
-  <si>
-    <t>CO</t>
   </si>
   <si>
     <t>15667</t>
@@ -167,9 +164,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -507,7 +505,8 @@
   <dimension ref="A1:L26"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="3" width="9.06640625" style="1"/>
+    <col min="1" max="2" width="9.06640625" style="1"/>
+    <col min="3" max="3" width="9.06640625" style="2"/>
     <col min="4" max="4" width="16.33203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="9.06640625" style="1"/>
     <col min="6" max="6" width="16.33203125" style="1" customWidth="1"/>
@@ -563,8 +562,8 @@
       <c r="B2" s="1">
         <v>1993</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>18</v>
+      <c r="C2" s="2">
+        <v>57</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>5</v>
@@ -598,8 +597,8 @@
       <c r="B3" s="1">
         <v>1995</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>18</v>
+      <c r="C3" s="2">
+        <v>57</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>5</v>
@@ -628,7 +627,7 @@
         <v>11838</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.6">
@@ -638,8 +637,8 @@
       <c r="B4" s="1">
         <v>2005</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>18</v>
+      <c r="C4" s="2">
+        <v>57</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>5</v>
@@ -673,8 +672,8 @@
       <c r="B5" s="1">
         <v>2017</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>18</v>
+      <c r="C5" s="2">
+        <v>57</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>5</v>
@@ -703,7 +702,7 @@
         <v>17740</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.6">
@@ -713,8 +712,8 @@
       <c r="B6" s="1">
         <v>2018</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>18</v>
+      <c r="C6" s="2">
+        <v>57</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>5</v>
@@ -748,23 +747,23 @@
       <c r="B7" s="1">
         <v>1985</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2">
+        <v>57</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="I7" s="1">
         <v>7371</v>
@@ -783,23 +782,23 @@
       <c r="B8" s="1">
         <v>1993</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2">
+        <v>57</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="I8" s="1">
         <v>7439</v>
@@ -818,23 +817,23 @@
       <c r="B9" s="1">
         <v>2005</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2">
+        <v>57</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="I9" s="1">
         <v>6383</v>
@@ -853,23 +852,23 @@
       <c r="B10" s="1">
         <v>2018</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2">
+        <v>57</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="I10" s="1">
         <v>4551</v>
@@ -888,23 +887,23 @@
       <c r="B11" s="1">
         <v>1985</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>18</v>
+      <c r="C11" s="2">
+        <v>57</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I11" s="1">
         <v>4225649</v>
@@ -923,23 +922,23 @@
       <c r="B12" s="1">
         <v>1993</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>18</v>
+      <c r="C12" s="2">
+        <v>57</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I12" s="1">
         <v>4945448</v>
@@ -958,23 +957,23 @@
       <c r="B13" s="1">
         <v>2005</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>18</v>
+      <c r="C13" s="2">
+        <v>57</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I13" s="1">
         <v>6840116</v>
@@ -993,23 +992,23 @@
       <c r="B14" s="1">
         <v>2018</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>18</v>
+      <c r="C14" s="2">
+        <v>57</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I14" s="1">
         <v>7181469</v>
@@ -1028,23 +1027,23 @@
       <c r="B15" s="1">
         <v>1775</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>18</v>
+      <c r="C15" s="2">
+        <v>57</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I15" s="1">
         <v>16233</v>
@@ -1056,7 +1055,7 @@
         <v>32</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.6">
@@ -1066,23 +1065,23 @@
       <c r="B16" s="1">
         <v>1800</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>18</v>
+      <c r="C16" s="2">
+        <v>57</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I16" s="1">
         <v>21964</v>
@@ -1094,7 +1093,7 @@
         <v>44</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.6">
@@ -1104,23 +1103,23 @@
       <c r="B17" s="1">
         <v>1832</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>18</v>
+      <c r="C17" s="2">
+        <v>57</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I17" s="1">
         <v>28341</v>
@@ -1132,7 +1131,7 @@
         <v>57</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.6">
@@ -1142,23 +1141,23 @@
       <c r="B18" s="1">
         <v>1870</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>18</v>
+      <c r="C18" s="2">
+        <v>57</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I18" s="1">
         <v>40883</v>
@@ -1170,7 +1169,7 @@
         <v>82</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.6">
@@ -1180,23 +1179,23 @@
       <c r="B19" s="1">
         <v>1905</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>18</v>
+      <c r="C19" s="2">
+        <v>57</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I19" s="1">
         <v>100000</v>
@@ -1208,7 +1207,7 @@
         <v>200</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.6">
@@ -1218,23 +1217,23 @@
       <c r="B20" s="1">
         <v>1912</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>18</v>
+      <c r="C20" s="2">
+        <v>57</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I20" s="1">
         <v>121257</v>
@@ -1246,7 +1245,7 @@
         <v>243</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.6">
@@ -1256,23 +1255,23 @@
       <c r="B21" s="1">
         <v>1918</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>18</v>
+      <c r="C21" s="2">
+        <v>57</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I21" s="1">
         <v>143994</v>
@@ -1284,7 +1283,7 @@
         <v>288</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.6">
@@ -1294,23 +1293,23 @@
       <c r="B22" s="1">
         <v>1928</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>18</v>
+      <c r="C22" s="2">
+        <v>57</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I22" s="1">
         <v>235702</v>
@@ -1322,7 +1321,7 @@
         <v>471</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.6">
@@ -1332,23 +1331,23 @@
       <c r="B23" s="1">
         <v>1938</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>18</v>
+      <c r="C23" s="2">
+        <v>57</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I23" s="1">
         <v>325650</v>
@@ -1360,7 +1359,7 @@
         <v>651</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.6">
@@ -1370,23 +1369,23 @@
       <c r="B24" s="1">
         <v>1951</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>18</v>
+      <c r="C24" s="2">
+        <v>57</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I24" s="1">
         <v>715250</v>
@@ -1398,7 +1397,7 @@
         <v>1430</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.6">
@@ -1408,23 +1407,23 @@
       <c r="B25" s="1">
         <v>1964</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>18</v>
+      <c r="C25" s="2">
+        <v>57</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I25" s="1">
         <v>1697311</v>
@@ -1436,7 +1435,7 @@
         <v>3395</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.6">
@@ -1446,23 +1445,23 @@
       <c r="B26" s="1">
         <v>1973</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>18</v>
+      <c r="C26" s="2">
+        <v>57</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I26" s="1">
         <v>2855065</v>
@@ -1474,7 +1473,7 @@
         <v>5710</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
